--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R338-ModaliteAccueil.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R338-ModaliteAccueil.xlsx
@@ -118,195 +118,198 @@
     <t>Count</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Accueil séquentiel accepté</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Prise en charge directe SMUR</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>En présentiel</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Téléconsultation</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Visite à domicile</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Prise en charge sans rendez-vous</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Accueil anonyme</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Accueil réservé aux femmes</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Participation aux gardes/astreintes</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Téléexpertise en moins de 24h</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Téléexpertise en moins de 7 jours</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Téléexpertise en plus de 7 jours</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Admission directe non programmée - personne âgée (PA)</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Télésoin</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Consultation dans des locaux dédiés - personnes en situation de handicap (PH)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Consultation sans locaux dédiés - personnes en situation de handicap (PH)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>HandiBloc</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Intra-hospitalier</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Extra-hospitalier</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Accueil séquentiel accepté</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Prise en charge directe SMUR</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>En présentiel</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Téléconsultation</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Visite à domicile</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Prise en charge sans rendez-vous</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>Accueil anonyme</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>Accueil réservé aux femmes</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>Participation aux gardes/astreintes</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Téléexpertise en moins de 24h</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Téléexpertise en moins de 7 jours</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Téléexpertise en plus de 7 jours</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Admission directe non programmée - personne âgée (PA)</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Télésoin</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Consultation dans des locaux dédiés - personnes en situation de handicap (PH)</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Consultation sans locaux dédiés - personnes en situation de handicap (PH)</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>HandiBloc</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Intra-hospitalier</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Extra-hospitalier</t>
-  </si>
-  <si>
     <t>Accueil en unité protégée</t>
   </si>
   <si>
@@ -326,9 +329,6 @@
   </si>
   <si>
     <t>Autodialyse simple</t>
-  </si>
-  <si>
-    <t>24</t>
   </si>
   <si>
     <t>Autodialyse assistée</t>
@@ -991,10 +991,10 @@
         <v>58</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -1003,10 +1003,10 @@
         <v>58</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2"/>
     </row>
@@ -1015,10 +1015,10 @@
         <v>58</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="2"/>
     </row>
@@ -1027,10 +1027,10 @@
         <v>58</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D24" s="2"/>
     </row>
@@ -1039,7 +1039,7 @@
         <v>58</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>105</v>
